--- a/data/quality_report.xlsx
+++ b/data/quality_report.xlsx
@@ -512,7 +512,7 @@
         <v>15.93</v>
       </c>
       <c r="E2" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>132.56</v>
@@ -524,7 +524,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         <v>17.36</v>
       </c>
       <c r="E3" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>135.9</v>
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -574,7 +574,7 @@
         <v>16.82</v>
       </c>
       <c r="E4" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>139.69</v>
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -605,7 +605,7 @@
         <v>21.57</v>
       </c>
       <c r="E5" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>132.22</v>
@@ -617,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>18.29</v>
       </c>
       <c r="E6" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>131.5</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -667,7 +667,7 @@
         <v>17.24</v>
       </c>
       <c r="E7" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>133.22</v>
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -698,7 +698,7 @@
         <v>17.63</v>
       </c>
       <c r="E8" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>159.19</v>
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -729,7 +729,7 @@
         <v>18.12</v>
       </c>
       <c r="E9" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>152.61</v>
@@ -741,7 +741,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -760,7 +760,7 @@
         <v>21.02</v>
       </c>
       <c r="E10" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>135.92</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -791,7 +791,7 @@
         <v>18.49</v>
       </c>
       <c r="E11" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>134.19</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -822,7 +822,7 @@
         <v>17.81</v>
       </c>
       <c r="E12" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>136.9</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -853,7 +853,7 @@
         <v>17.91</v>
       </c>
       <c r="E13" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>136.68</v>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -884,7 +884,7 @@
         <v>19.94</v>
       </c>
       <c r="E14" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>126.07</v>
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -915,7 +915,7 @@
         <v>20.74</v>
       </c>
       <c r="E15" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>126.65</v>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -946,7 +946,7 @@
         <v>20.66</v>
       </c>
       <c r="E16" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>135.04</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -977,7 +977,7 @@
         <v>20.02</v>
       </c>
       <c r="E17" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>126.33</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1008,7 +1008,7 @@
         <v>20.42</v>
       </c>
       <c r="E18" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>135.15</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1039,7 +1039,7 @@
         <v>21.14</v>
       </c>
       <c r="E19" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>133.67</v>
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1070,7 +1070,7 @@
         <v>21.21</v>
       </c>
       <c r="E20" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>134.8</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1101,7 +1101,7 @@
         <v>19.41</v>
       </c>
       <c r="E21" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>126.43</v>
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1132,7 +1132,7 @@
         <v>20.74</v>
       </c>
       <c r="E22" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>128.97</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1163,7 +1163,7 @@
         <v>20.98</v>
       </c>
       <c r="E23" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>131.66</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1194,7 +1194,7 @@
         <v>24</v>
       </c>
       <c r="E24" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>133.08</v>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1225,7 +1225,7 @@
         <v>24.68</v>
       </c>
       <c r="E25" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>131.46</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
